--- a/MIAPPE_extension/MIAFPE.xlsx
+++ b/MIAPPE_extension/MIAFPE.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.grygosch\Desktop\FAIRAgro\datalab\metadata\MIAPPEext\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.grygosch\Desktop\FAIRAgro\developement\MIAFPE\MIAPPE_extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03D0889C-9785-46FC-BDB4-F93E44000514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687AB3E2-D1BA-4CE3-8C41-BF7179FE4FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{683B011A-2F29-4327-800E-1A9041681AF0}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{683B011A-2F29-4327-800E-1A9041681AF0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Metadata" sheetId="6" r:id="rId1"/>
-    <sheet name="Investigation" sheetId="1" r:id="rId2"/>
-    <sheet name="Study" sheetId="3" r:id="rId3"/>
-    <sheet name="Person" sheetId="2" r:id="rId4"/>
+    <sheet name="Investigation" sheetId="10" r:id="rId1"/>
+    <sheet name="Study" sheetId="3" r:id="rId2"/>
+    <sheet name="Observation Unit" sheetId="7" r:id="rId3"/>
+    <sheet name="Observed Variable" sheetId="8" r:id="rId4"/>
     <sheet name="Sensor" sheetId="4" r:id="rId5"/>
-    <sheet name="Data fIle" sheetId="5" r:id="rId6"/>
+    <sheet name="Platform" sheetId="9" r:id="rId6"/>
+    <sheet name="Data file" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="174">
   <si>
     <t>Field</t>
   </si>
@@ -55,18 +56,9 @@
     <t>Format</t>
   </si>
   <si>
-    <t>Values</t>
-  </si>
-  <si>
     <t>Value</t>
   </si>
   <si>
-    <t>Mandetory</t>
-  </si>
-  <si>
-    <t>Investigation title</t>
-  </si>
-  <si>
     <t>Investigation unique ID</t>
   </si>
   <si>
@@ -82,12 +74,6 @@
     <t>License</t>
   </si>
   <si>
-    <t>MIAPPE version</t>
-  </si>
-  <si>
-    <t>Assiociated publicatiopn</t>
-  </si>
-  <si>
     <t>Identifier comprising the unique name of the institution/database hosting the submission of the investigation data, and the accession number of the investigation in that institution.</t>
   </si>
   <si>
@@ -130,38 +116,521 @@
     <t>DOI</t>
   </si>
   <si>
-    <t>Version</t>
-  </si>
-  <si>
-    <t>Metadata unique ID</t>
-  </si>
-  <si>
-    <t>URI</t>
-  </si>
-  <si>
-    <t>Ontologies</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>l</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>o</t>
-  </si>
-  <si>
-    <t>welt</t>
+    <r>
+      <t>Study unique ID</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <t>Study title*</t>
+  </si>
+  <si>
+    <t>Study description</t>
+  </si>
+  <si>
+    <t>Start date of study*</t>
+  </si>
+  <si>
+    <t>End date of study</t>
+  </si>
+  <si>
+    <t>Contact institution*</t>
+  </si>
+  <si>
+    <t>Geographic location (country)*</t>
+  </si>
+  <si>
+    <t>Experimental site name*</t>
+  </si>
+  <si>
+    <t>Geographic location (latitude)</t>
+  </si>
+  <si>
+    <t>Geographic location (longitude)</t>
+  </si>
+  <si>
+    <t>Geographic location (altitude)</t>
+  </si>
+  <si>
+    <t>Description of the experimental design*</t>
+  </si>
+  <si>
+    <t>Type of experimental design</t>
+  </si>
+  <si>
+    <t>Observation unit level hierarchy</t>
+  </si>
+  <si>
+    <t>Observation unit description*</t>
+  </si>
+  <si>
+    <t>Description of growth facility*</t>
+  </si>
+  <si>
+    <t>Type of growth facility</t>
+  </si>
+  <si>
+    <t>Cultural practices</t>
+  </si>
+  <si>
+    <t>Map of experimental design</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Unique identifier comprising the name or identifier for the institution/database hosting the submission of the study data, and the identifier of the study in that institution.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>If the study has no official unique ID, assign your own following the schema: study_1, study_2, study_..., study_n.</t>
+    </r>
+  </si>
+  <si>
+    <t>Human-readable text summarising the study</t>
+  </si>
+  <si>
+    <t>Human-readable text describing the study</t>
+  </si>
+  <si>
+    <t>Date and, if relevant, time when the experiment started</t>
+  </si>
+  <si>
+    <t>Date and, if relevant, time when the experiment ended</t>
+  </si>
+  <si>
+    <t>Name and address of the institution responsible for the study.</t>
+  </si>
+  <si>
+    <t>The country where the experiment took place, either as a full name or preferably as a 2-letter code.</t>
+  </si>
+  <si>
+    <t>The name of the natural site, experimental field, greenhouse, phenotyping facility, etc. where the experiment took place.</t>
+  </si>
+  <si>
+    <t>Latitude of the experimental site in degrees, in decimal format.</t>
+  </si>
+  <si>
+    <t>Longitude of the experimental site in degrees, in decimal format.</t>
+  </si>
+  <si>
+    <t>Altitude of the experimental site, provided in metres (m).</t>
+  </si>
+  <si>
+    <t>Short description of the experimental design, possibly including statistical design. In specific cases, e.g. legacy datasets or data computed from several studies, the experimental design can be "unknown"/"NA", "aggregated/reduced data", or simply 'none'.</t>
+  </si>
+  <si>
+    <t>Type of experimental  design of the study, in the form of an accession number from the Crop Ontology.</t>
+  </si>
+  <si>
+    <t>Hierarchy of the different levels of repetitions between each others</t>
+  </si>
+  <si>
+    <t>General description of the observation units in the study.</t>
+  </si>
+  <si>
+    <t>Short description of the facility in which the study was carried out.</t>
+  </si>
+  <si>
+    <t>Type of growth facility in which the study was carried out, in the form of an accession number from the Crop Ontology.</t>
+  </si>
+  <si>
+    <t>General description of the cultural practices of the study.</t>
+  </si>
+  <si>
+    <t>Representation of the experimental design.</t>
+  </si>
+  <si>
+    <t>EBI:12345678; 
+http://phenome-fppn.fr/maugio/2013/t2351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2002 evaluation of flowering time for a panel of 375 maize lines at the experimental station of Maugio (France). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2002 evaluation of male and female flowering time for a panel of 375 maize lines representing the worldwide genetic diversity at the experimental station of Maugio, France. </t>
+  </si>
+  <si>
+    <t>2002-04-04
+2006-09-27T10:23:21+00:00</t>
+  </si>
+  <si>
+    <t>UMR de Génétique Végétale, INRA – Université Paris-Sud – CNRS, Gif-sur-Yvette, France</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>INRA, UE Diascope - Chemin de Mezouls - Domaine expérimental de Melgueil - 34130 Mauguio - France</t>
+  </si>
+  <si>
+    <t>+43.619264</t>
+  </si>
+  <si>
+    <t>+3.967454</t>
+  </si>
+  <si>
+    <t>100 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lines were repeated twice at each location using a complete block design. In order to limit competition effects, each block was organized into four sub-blocks corresponding to earliness groups based on a priori information. </t>
+  </si>
+  <si>
+    <t>CO_715:0000145</t>
+  </si>
+  <si>
+    <t>block&gt;rep&gt;plot</t>
+  </si>
+  <si>
+    <t>Observation units consisted in individual plots themselves consisting of a row of 15 plants at a density of approximately six plants per square meter.
+NA</t>
+  </si>
+  <si>
+    <t>field environment condition
+NA</t>
+  </si>
+  <si>
+    <t>CO_715:0000162</t>
+  </si>
+  <si>
+    <t>Irrigation was applied according needs during summer to prevent water stress.</t>
+  </si>
+  <si>
+    <t>https://urgi.versailles.inra.fr/files/ephesis/181000503/181000503_plan.xls</t>
+  </si>
+  <si>
+    <t>Country name or 2-letter code (ISO 3166)</t>
+  </si>
+  <si>
+    <t>Degrees in the decimal format (ISO 6709)</t>
+  </si>
+  <si>
+    <t>Numeric + unit abbreviation</t>
+  </si>
+  <si>
+    <t>Crop Ontology term (subclass of "CO_715:0000003")</t>
+  </si>
+  <si>
+    <t>Formatted text (level&gt;level)</t>
+  </si>
+  <si>
+    <t>Crop Ontology term (subclass of "CO_715:0000005")</t>
+  </si>
+  <si>
+    <t>URL or File name (of gis or tabular file like csv or tsv)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Values </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(add rows if necessary)</t>
+    </r>
+  </si>
+  <si>
+    <t>Study unique ID*</t>
+  </si>
+  <si>
+    <t>Data file link*</t>
+  </si>
+  <si>
+    <t>Data file description*</t>
+  </si>
+  <si>
+    <t>Data file version*</t>
+  </si>
+  <si>
+    <t>Semicolon-separated list of (internal) study identifiers (cross-referencing to study worksheet) to which the file belongs.</t>
+  </si>
+  <si>
+    <t>Link to the data file (or digital object) in a public database or in a persistent institutional repository; or identifier of the data file when submitted together with the MIAPPE submission.</t>
+  </si>
+  <si>
+    <t>Description of the format of the data file. May be a standard file format name, or a description of organization of the data in a tabular file.</t>
+  </si>
+  <si>
+    <t>The version of the dataset (the actual data).</t>
+  </si>
+  <si>
+    <t>study_1; study_2</t>
+  </si>
+  <si>
+    <t>http://www.ebi.ac.uk/arrayexpress/experiments/E-GEOD-32551/</t>
+  </si>
+  <si>
+    <t>FASTA
+tab-delimited
+column headers headers: 1. A 2. B 3. C</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>List</t>
+  </si>
+  <si>
+    <t>URL or File name</t>
+  </si>
+  <si>
+    <t>Software version number</t>
+  </si>
+  <si>
+    <t>EBI:12345678</t>
+  </si>
+  <si>
+    <t>Investigation title*</t>
+  </si>
+  <si>
+    <t>Adaptation of Maize to Temperate Climates: Mid-Density Genome-Wide Association Genetics and Diversity Patterns Reveal Key Genomic Regions, with a Major Contribution of the Vgt2 (ZCN8) Locus.</t>
+  </si>
+  <si>
+    <t>The migration of maize from tropical to temperate climates was accompanied by a dramatic evolution in flowering time. To gain insight into the genetic architecture of this adaptive trait, we conducted a 50K SNP-based genome-wide association and diversity investigation on a panel of tropical and temperate American and European representatives.</t>
+  </si>
+  <si>
+    <t>2013-02-25</t>
+  </si>
+  <si>
+    <t>CC BY-SA 4.0, Unreported</t>
+  </si>
+  <si>
+    <t>MIAPPE version*</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Associated publication</t>
+  </si>
+  <si>
+    <t>doi:10.1371/journal.pone.0071377</t>
+  </si>
+  <si>
+    <t>Biological Material ID*</t>
+  </si>
+  <si>
+    <t>Observation unit ID*</t>
+  </si>
+  <si>
+    <t>Observation unit type*</t>
+  </si>
+  <si>
+    <t>External ID</t>
+  </si>
+  <si>
+    <t>Spatial distribution</t>
+  </si>
+  <si>
+    <t>Observation Unit factor value</t>
+  </si>
+  <si>
+    <t>Semicolon-separated list of (internal) study identifiers (cross-referencing to study worksheet) to which the observation unit belongs to.</t>
+  </si>
+  <si>
+    <t>Biological Material identifier (cross-referencing to Biological Material worksheet) corresponding to the organism(s) being observed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier used to identify the observation unit in data files containing the values observed or measured on that unit. Must be locally unique. </t>
+  </si>
+  <si>
+    <t>Type of observation unit in textual form, usually one of the following: study, block, sub-block, plot, sub-plot, pot, plant. 
+Use of other observation unit types is possible but not recommended. 
+The observation unit type cannot be used to indicate sub-plant levels. However, observations can still be made on the sub-plant level, as long as the details are indicated in the associated observed variable (see observed variables).
+Alternatively, it is possible to use samples for more detailed tracing of sub-plant units, attaching the observations to them instead.</t>
+  </si>
+  <si>
+    <t>Identifier for the observation unit in a persistent repository, comprises the name of the repository and the identifier of the observation unit therein. The EBI Biosamples repository can be used. URI are recommended when possible.</t>
+  </si>
+  <si>
+    <t>Type and value of a spatial coordinate (georeference or relative) or level of observation (plot 45, subblock 7, block 2) provided as a key-value pair of the form type:value. Levels of observation must be consistent with those listed in the Study section.</t>
+  </si>
+  <si>
+    <t>List of values for each factor applied to the observation unit.</t>
+  </si>
+  <si>
+    <t>study_1</t>
+  </si>
+  <si>
+    <t>1; 2</t>
+  </si>
+  <si>
+    <t>plot:894</t>
+  </si>
+  <si>
+    <t>plot</t>
+  </si>
+  <si>
+    <t>Biosamples:SAMEA4202911</t>
+  </si>
+  <si>
+    <t>latitude:+2.341; row:4 ; X:3; Y:6; Xm:35; Ym:65; block:1; plot:894</t>
+  </si>
+  <si>
+    <t>Watered</t>
+  </si>
+  <si>
+    <t>Formatted text (Key:value)</t>
+  </si>
+  <si>
+    <t>Variable ID*</t>
+  </si>
+  <si>
+    <t>Variable name</t>
+  </si>
+  <si>
+    <t>Variable accession number</t>
+  </si>
+  <si>
+    <t>Trait*</t>
+  </si>
+  <si>
+    <t>Trait accession number</t>
+  </si>
+  <si>
+    <t>Method*</t>
+  </si>
+  <si>
+    <t>Method accession number</t>
+  </si>
+  <si>
+    <t>Method description</t>
+  </si>
+  <si>
+    <t>Reference associated to the method</t>
+  </si>
+  <si>
+    <t>Scale*</t>
+  </si>
+  <si>
+    <t>Scale accession number</t>
+  </si>
+  <si>
+    <t>Time scale</t>
+  </si>
+  <si>
+    <t>Semicolon-separated list of (internal) study identifiers (cross-referencing to study worksheet) for which the variable was observed.</t>
+  </si>
+  <si>
+    <t>Code used to identify the variable in the data file. We recommend using a variable definition from the Crop Ontology where possible. Otherwise, the Crop Ontology naming convention is recommended: &lt;trait abbreviation&gt;_&lt;method abbreviation&gt;_&lt;scale abbreviation&gt;). A variable ID must be unique within a given investigation.</t>
+  </si>
+  <si>
+    <t>Name of the variable.</t>
+  </si>
+  <si>
+    <t>Accession number of the variable in the Crop Ontology</t>
+  </si>
+  <si>
+    <t>Name of the (plant or environmental) trait under observation</t>
+  </si>
+  <si>
+    <t>Accession number of the trait in a suitable controlled vocabulary (Crop Ontology, Trait Ontology).</t>
+  </si>
+  <si>
+    <t>Name of the method of observation</t>
+  </si>
+  <si>
+    <t>Accession number of the method in a suitable controlled vocabulary (Crop Ontology, Trait Ontology).</t>
+  </si>
+  <si>
+    <t>Textual description of the method, which may extend a method defined in an external reference with specific parameters, e.g. growth stage, inoculation precise organ (leaf number)</t>
+  </si>
+  <si>
+    <t>URI/DOI of reference describing the method.</t>
+  </si>
+  <si>
+    <t>Name of the scale associated with the variable</t>
+  </si>
+  <si>
+    <t>Accession number of the scale in a suitable controlled vocabulary (Crop Ontology).</t>
+  </si>
+  <si>
+    <t>Name of the scale or unit of time with which observations of this type were recorded in the data file (for time series studies).</t>
+  </si>
+  <si>
+    <t>Ant_Cmp_Cday</t>
+  </si>
+  <si>
+    <t>Anthesis computed in growing degree days</t>
+  </si>
+  <si>
+    <t>CO_322:0000794</t>
+  </si>
+  <si>
+    <t>Anthesis time
+Reproductive growth time</t>
+  </si>
+  <si>
+    <t>CO_322:0000030
+TO:0000366</t>
+  </si>
+  <si>
+    <t>Growing degree days to anthesis</t>
+  </si>
+  <si>
+    <t>CO_322:0000189</t>
+  </si>
+  <si>
+    <t>Days to anthesis for male flowering was measured in thermal time (GDD: growing degree-days) according to Ritchie J, NeSmith D (1991;Temperature and crop development. Modeling plant and soil systems American Society of Agronomy Madison, Wisconsin USA) with TBASE=8°C and T0=30°C.
+Plant height was measured at 5 years with a ruler, one year after Botritis inoculation.</t>
+  </si>
+  <si>
+    <t>http://doi.org/10.2134/agronmonogr31.c2</t>
+  </si>
+  <si>
+    <t>°C day</t>
+  </si>
+  <si>
+    <t>CO_322:0000510</t>
+  </si>
+  <si>
+    <t>Growing degree day (GDD)
+Date/Time</t>
+  </si>
+  <si>
+    <t>Crop Ontology term</t>
+  </si>
+  <si>
+    <t>Term from Plant Trait Ontology, Crop Ontology, or XML Environment Ontology</t>
+  </si>
+  <si>
+    <t>URI or DOI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+  </numFmts>
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,16 +644,109 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFE2EFD9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -207,24 +769,218 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Link" xfId="2" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard 2" xfId="1" xr:uid="{A0DE211B-617F-4037-A99D-2A5DD796F656}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -555,56 +1311,145 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E7B6DE-3256-49F8-9EF8-9DBB3A859904}">
-  <dimension ref="A1:D6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80AACCA0-BD6F-4862-8702-39FAEB99FCBF}">
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B1" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="32" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="D1" s="32" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="E1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="229.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="34"/>
+      <c r="C2" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="255" x14ac:dyDescent="0.25">
+      <c r="A3" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="34"/>
+      <c r="C3" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
+      <c r="B4" s="34"/>
+      <c r="C4" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="34"/>
+      <c r="C5" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="37">
+        <v>41260</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="34"/>
+      <c r="C6" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="191.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="34"/>
+      <c r="C7" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" s="34"/>
+      <c r="C8" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="153" x14ac:dyDescent="0.25">
+      <c r="A9" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="34"/>
+      <c r="C9" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -613,310 +1458,1248 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D589C1A-4726-4556-9516-7B769CECDDE0}">
-  <dimension ref="A1:F9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC197394-8E0A-48DF-BF49-5FE6B8D3A54C}">
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="27.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="34.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="29.85546875" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="11.42578125" style="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="51" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T1" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="357" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="S2" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="T2" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="306" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="11">
+        <v>37587</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="S3" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="T3" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="D4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
+      <c r="F4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="S4" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="T4" s="15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="18"/>
+      <c r="S5" s="18"/>
+      <c r="T5" s="19"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="40"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="19"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="40"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="18"/>
+      <c r="S7" s="18"/>
+      <c r="T7" s="19"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" s="40"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="18"/>
+      <c r="S8" s="18"/>
+      <c r="T8" s="19"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="40"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="18"/>
+      <c r="S9" s="18"/>
+      <c r="T9" s="20"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="40"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="18"/>
+      <c r="S10" s="18"/>
+      <c r="T10" s="17"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="41"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="18"/>
+      <c r="T11" s="17"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:A11"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="T3" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC197394-8E0A-48DF-BF49-5FE6B8D3A54C}">
-  <dimension ref="A1:A5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B27F2740-14D9-47DE-BABF-7AA6A69BF8FF}">
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" ht="51" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B2" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="84" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B3" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="36" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
+      <c r="B4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="42"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="42"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="42"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="42"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="42"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="43"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:A11"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15E3D645-BDAE-4C07-97F2-8721852646BD}">
-  <dimension ref="A1:A5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A93501-44C1-4A95-8E3F-53204ED54327}">
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14" ht="51" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="I1" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="M1" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="N1" s="25" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B2" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="29" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B3" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="K3" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="102" x14ac:dyDescent="0.25">
+      <c r="A4" s="29" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
+      <c r="B4" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="42"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="42"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="42"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="42"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="42"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="43"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:A11"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="K3" r:id="rId1" xr:uid="{00000000-0004-0000-0D00-000000000000}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE2ED500-E32B-426B-8C81-BE5153830C8D}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="21"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
+      <c r="B4" s="22"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="42"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="42"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="42"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="42"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="42"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="43"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:A11"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{937412D9-07DA-457F-B1AF-F422D367EA69}">
-  <dimension ref="A1:A5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB6042F7-552B-4B35-96BD-BF5879C5985A}">
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="21"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
+      <c r="B4" s="22"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="42"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="42"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="42"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="42"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="42"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="43"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:A11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{937412D9-07DA-457F-B1AF-F422D367EA69}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="229.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="42"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="42"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="42"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="42"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="42"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="43"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:A11"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/MIAPPE_extension/MIAFPE.xlsx
+++ b/MIAPPE_extension/MIAFPE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.grygosch\Desktop\FAIRAgro\developement\MIAFPE\MIAPPE_extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687AB3E2-D1BA-4CE3-8C41-BF7179FE4FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38944192-36E0-44C6-942C-EFA4F3EDBF49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{683B011A-2F29-4327-800E-1A9041681AF0}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{683B011A-2F29-4327-800E-1A9041681AF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Investigation" sheetId="10" r:id="rId1"/>

--- a/MIAPPE_extension/MIAFPE.xlsx
+++ b/MIAPPE_extension/MIAFPE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.grygosch\Desktop\FAIRAgro\developement\MIAFPE\MIAPPE_extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38944192-36E0-44C6-942C-EFA4F3EDBF49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBAA67C9-9F4D-49E3-A450-14CA24F2691C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{683B011A-2F29-4327-800E-1A9041681AF0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{683B011A-2F29-4327-800E-1A9041681AF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Investigation" sheetId="10" r:id="rId1"/>
